--- a/tests/assets/golden/openpyxl/test_template_1_filled.xlsx
+++ b/tests/assets/golden/openpyxl/test_template_1_filled.xlsx
@@ -180,7 +180,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableTest" displayName="TableTest" ref="A1:E6" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E6"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Col1"/>
     <tableColumn id="2" name="Col2"/>
